--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,31 +480,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>711314367</v>
+        <v>8071127858</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>@ekaterinapavlidi</t>
+          <t>@nlo_cln</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>79280127273</t>
+          <t>79969169607</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>жен</t>
+          <t>муж</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>👨35–44</t>
+          <t>🧑25–34</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>СПб</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -519,118 +519,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Другое: Hi</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>speak</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-26 07:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>8071127858</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>@nlo_cln</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>79969169607</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>📱18–24</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Мск</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-03-26 02:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>8143298121</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>@None</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>77719911141</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>жен</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>👴45+</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Другая_страна</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>16-17</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>exams</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-03-26 02:54</t>
+          <t>2026-03-26 13:39</t>
         </is>
       </c>
     </row>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,67 +474,17 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>child_barrier</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>preferences</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>reg_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>8071127858</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>@nlo_cln</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>79969169607</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>🧑25–34</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>СПб</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>speech</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Другое: Hi</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4-6</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>speak</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-03-26 13:39</t>
         </is>
       </c>
     </row>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,64 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>reg_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8071127858</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@nlo_cln</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>79969169607</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>📱18–24</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>СПб</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16-17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Другое: Baggage</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:09</t>
         </is>
       </c>
     </row>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -509,12 +509,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>📱18–24</t>
+          <t>👨35–44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>СПб</t>
+          <t>Другая_страна</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -522,8 +522,16 @@
           <t>ребенок</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>work</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Другое: Sksksk</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>16-17</t>
@@ -531,15 +539,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>exams</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Другое: Baggage</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>Другое: Jail</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>2026-03-27 16:09</t>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,76 +485,6 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>reg_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>8071127858</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>@nlo_cln</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>79969169607</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>👨35–44</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Другая_страна</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>work</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Другое: Sksksk</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>16-17</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>exams</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Другое: Jail</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-03-27 16:09</t>
         </is>
       </c>
     </row>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,133 @@
         <is>
           <t>reg_date</t>
         </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ticket_number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8071127858</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@nlo_cln</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>79969169607</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>👨35–44</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>movies</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Другое: He’s</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>checklists</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:02</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8143298121</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>77719911141</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>👨35–44</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>movies</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>motivation</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>reels</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:03</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1002</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,105 +514,48 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>👨35–44</t>
+          <t>✨35–44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Мск</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>movies</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Другое: He’s</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>looking</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Другое: Smile</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>checklists</t>
+          <t>reels</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-28 00:02</t>
+          <t>2026-03-30 17:55</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>1001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>8143298121</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>@None</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>77719911141</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>👨35–44</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>РФ</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>movies</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>motivation</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>reels</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-03-28 00:03</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>1002</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,71 +491,6 @@
         <is>
           <t>ticket_number</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>8071127858</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>@nlo_cln</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>79969169607</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>✨35–44</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Мск</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10-12</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>looking</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Другое: Smile</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>reels</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-03-30 17:55</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,71 @@
         <is>
           <t>ticket_number</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8071127858</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@nlo_cln</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>79969169607</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Другая_страна</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>speak</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>motivation</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>reels</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-03-30 18:10</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>муж</t>
+          <t>жен</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -519,31 +519,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Другая_страна</t>
+          <t>Мск</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4-6</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>speak</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>motivation</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>movies</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Другое: Guy</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>reels</t>
@@ -551,11 +547,72 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-30 18:10</t>
+          <t>2026-03-30 18:17</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>1001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8143298121</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>77719911141</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>✨18–24</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Другая_страна</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>child_help</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>format</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-03-30 18:18</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1002</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,20 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>importance</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>reg_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ticket_number</t>
         </is>
@@ -509,7 +519,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>жен</t>
+          <t>муж</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -524,22 +534,34 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>взрослый</t>
+          <t>ребенок</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>movies</t>
+          <t>exams</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Другое: Guy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13-15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Другое: Jamal’s</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>reels</t>
@@ -547,72 +569,21 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-30 18:17</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+          <t>infinity</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
         <v>1001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>8143298121</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>@None</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>77719911141</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>✨18–24</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Другая_страна</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>child_help</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>format</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-03-30 18:18</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>1002</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -534,17 +534,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ребенок</t>
+          <t>взрослый</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>exams</t>
+          <t>грамматика</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>деньги</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -564,17 +564,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>reels</t>
+          <t>рилсы</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>infinity</t>
+          <t>9000_15000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>результат</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -524,52 +524,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>✨35–44</t>
+          <t>✨18–24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Мск</t>
+          <t>РФ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>грамматика</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>деньги</t>
-        </is>
-      </c>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13-15</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>разведка</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Другое: Jamal’s</t>
+          <t>другое</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>рилсы</t>
+          <t>чек-листы</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9000_15000</t>
+          <t>15000+</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,7 +571,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-03-30 20:00</t>
+          <t>2026-03-30 21:43</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,81 +501,6 @@
         <is>
           <t>ticket_number</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>8071127858</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>@nlo_cln</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>79969169607</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>✨18–24</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>РФ</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4-6</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>разведка</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>другое</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>чек-листы</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>15000+</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>результат</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-03-30 21:43</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,146 @@
         <is>
           <t>ticket_number</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5334917635</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@cocaerr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✨18–24</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8071127858</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@nlo_cln</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>79969169607</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13-15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>разведка</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:20</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,10 +494,15 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>subscriber</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>reg_date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ticket_number</t>
         </is>
@@ -505,141 +510,89 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5334917635</v>
+        <v>8071127858</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>@cocaerr</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>@nlo_cln</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>+79969169607</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>муж</t>
+          <t>жен</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>✨18–24</t>
+          <t>✨45+</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Другая_страна</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>взрослый</t>
+          <t>ребенок</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>путешествия</t>
+          <t>говорение</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>страх</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>переезд</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Другое: ewgweg\</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>гайды</t>
+          <t>чек-листы</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2000-8000</t>
+          <t>бесплатно</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>результат</t>
+          <t>отзывы</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-03-30 22:20</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>8071127858</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>@nlo_cln</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>79969169607</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>✨35–44</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Мск</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13-15</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>разведка</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>время</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>гайды</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2000-8000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>время</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-03-30 22:20</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:23</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
         <v>1001</v>
       </c>
     </row>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,90 +510,1284 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>66578182</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:59</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>174401763</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@OlgaVodyanova</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13-15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:13</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>385454770</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>@vicky_shomova</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>79161247769</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>сейчас</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:20</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>468444700</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>@erzhena_moglieva</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>79627175172</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>СПб</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Другое: Мы уже занимаемся английским языком в вашей школе ☺️</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>15000+</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:10</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>502957014</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>@Natalja_ta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>79117063105</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✨45+</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>СПб</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:42</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>590170268</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>@anastasia_propuskova</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>79817813120</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>СПб</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:28</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>700939186</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>79234240688</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Другое: Мы занимаемся</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:26</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>774244434</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>@anastasioca</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>79857794744</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>игры</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Другое: Ничего не мешает ) занимаемся ) ищем более удобный формат</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:39</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>837194297</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>@Kiriyiki</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>79283280068</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:57</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>866643274</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>@voevodinamarina</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>79374049190</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:05</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>895383725</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>@Anna_padalko1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>79286072201</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Другое: Уже занимается</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>9000-15000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:04</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>928756491</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>@ekaterina121289</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:08</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1155412866</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>@Tremaska</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>79260992058</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15000+</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:15</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1288940419</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>@Tsimbalistova_Ekaterina</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>79187643721</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:58</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5186300541</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>@yuliguma</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>79914348363</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>✨18–24</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>бесплатно</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:57</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7286528532</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>@propuskstasy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>79930737358</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>СПб</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>переезд</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>9000-15000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:44</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>8071127858</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>@nlo_cln</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>+79969169607</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>жен</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>✨45+</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Другая_страна</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>говорение</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>79969169607</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>муж</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ребёнок</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>чек-листы</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>время</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4-6</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>переезд</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Другое: ewgweg\</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>чек-листы</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>бесплатно</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>отзывы</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>недавно</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-03-31 14:23</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>1001</v>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-04-06 09:13</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1014</v>
       </c>
     </row>
   </sheetData>

--- a/results_export.xlsx
+++ b/results_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,27 +510,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66578182</v>
+        <v>15917434</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>@None</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>@FILL_9214</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>79887466712</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>жен</t>
+          <t>муж</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>✨35–44</t>
+          <t>✨25–34</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Мск</t>
+          <t>РФ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -540,7 +544,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>говорение</t>
+          <t>путешествия</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -553,7 +557,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>рилсы</t>
+          <t>гайды</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -563,7 +567,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>преподаватель</t>
+          <t>результат</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -573,18 +577,20 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-04-06 08:59</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>2026-04-08 17:00</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1035</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>174401763</v>
+        <v>66578182</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>@OlgaVodyanova</t>
+          <t>@None</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -605,41 +611,61 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13-15</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-04-06 07:13</t>
+          <t>2026-04-06 08:59</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>385454770</v>
+        <v>127195662</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>@vicky_shomova</t>
+          <t>@ZZalinaR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>79161247769</t>
+          <t>79172473881</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -654,7 +680,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Мск</t>
+          <t>Миллионник</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -666,7 +692,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -676,12 +702,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>страх</t>
+          <t>мотивация</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>гайды</t>
+          <t>акции</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -691,35 +717,35 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>преподаватель</t>
+          <t>результат</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>сейчас</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-04-06 08:20</t>
+          <t>2026-04-06 16:53</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1008</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>468444700</v>
+        <v>128317938</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>@erzhena_moglieva</t>
+          <t>@Evgeniya17panda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>79627175172</t>
+          <t>79101748821</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -734,31 +760,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>СПб</t>
+          <t>Мск</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>10-12</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>говорение</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Другое: Мы уже занимаемся английским языком в вашей школе ☺️</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>мотивация</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>гайды</t>
@@ -766,42 +788,38 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>15000+</t>
+          <t>2000-8000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>результат</t>
+          <t>преподаватель</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>давно</t>
+          <t>сейчас</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-04-06 07:10</t>
+          <t>2026-04-08 18:51</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1001</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>502957014</v>
+        <v>174401763</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>@Natalja_ta</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>79117063105</t>
-        </is>
-      </c>
+          <t>@OlgaVodyanova</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>жен</t>
@@ -809,78 +827,56 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>✨45+</t>
+          <t>✨35–44</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>СПб</t>
+          <t>Мск</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>путешествия</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>деньги</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13-15</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>гайды</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2000-8000</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>результат</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-04-06 10:42</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>1013</v>
-      </c>
+          <t>2026-04-06 07:13</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>590170268</v>
+        <v>308151640</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>@anastasia_propuskova</t>
+          <t>@Flisson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>79817813120</t>
+          <t>79517666330</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>жен</t>
+          <t>муж</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>СПб</t>
+          <t>Мск</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -900,12 +896,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>путешествия</t>
+          <t>работа</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>страх</t>
+          <t>деньги</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -913,7 +909,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>гайды</t>
+          <t>рилсы</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -928,30 +924,30 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>давно</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-04-06 08:28</t>
+          <t>2026-04-06 16:41</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1009</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>700939186</v>
+        <v>350567320</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>@None</t>
+          <t>@victor_i_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>79234240688</t>
+          <t>79650617788</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -961,36 +957,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>✨35–44</t>
+          <t>✨25–34</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>СПб</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>10-12</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>говорение</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Другое: Мы занимаемся</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>гайды</t>
@@ -1003,7 +995,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>время</t>
+          <t>результат</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1013,25 +1005,25 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-04-06 07:26</t>
+          <t>2026-04-06 12:42</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1002</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>774244434</v>
+        <v>359166974</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>@anastasioca</t>
+          <t>@Sadigova_lena</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>79857794744</t>
+          <t>79260799933</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1051,26 +1043,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4-6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>игры</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Другое: Ничего не мешает ) занимаемся ) ищем более удобный формат</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Другое: Ничего не мешает,я занимаюсь в вашей школе</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>акции</t>
@@ -1088,30 +1076,30 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>недавно</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-04-06 08:39</t>
+          <t>2026-04-06 16:50</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1010</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>837194297</v>
+        <v>385454770</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>@Kiriyiki</t>
+          <t>@vicky_shomova</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>79283280068</t>
+          <t>79161247769</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1126,7 +1114,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Мск</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1148,12 +1136,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>формат</t>
+          <t>страх</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>рилсы</t>
+          <t>гайды</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1168,30 +1156,30 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>давно</t>
+          <t>сейчас</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-04-06 07:57</t>
+          <t>2026-04-06 08:20</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>1004</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>866643274</v>
+        <v>468444700</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>@voevodinamarina</t>
+          <t>@erzhena_moglieva</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>79374049190</t>
+          <t>79627175172</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1206,7 +1194,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>СПб</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1228,7 +1216,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>деньги</t>
+          <t>Другое: Мы уже занимаемся английским языком в вашей школе ☺️</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1238,7 +1226,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2000-8000</t>
+          <t>15000+</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1248,30 +1236,30 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>недавно</t>
+          <t>давно</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-04-06 08:05</t>
+          <t>2026-04-06 07:10</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>895383725</v>
+        <v>502957014</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>@Anna_padalko1</t>
+          <t>@Natalja_ta</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>79286072201</t>
+          <t>79117063105</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1281,44 +1269,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>✨25–34</t>
+          <t>✨45+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Мск</t>
+          <t>СПб</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>7-9</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>говорение</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Другое: Уже занимается</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>акции</t>
+          <t>гайды</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9000-15000</t>
+          <t>2000-8000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1328,92 +1312,106 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>давно</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-04-06 08:04</t>
+          <t>2026-04-06 10:42</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>1005</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>928756491</v>
+        <v>514776160</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>@ekaterina121289</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>@ForeverEloy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>79652016676</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>жен</t>
+          <t>муж</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>✨35–44</t>
+          <t>✨18–24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Мск</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>10-12</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>школа</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>формат</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>экзамены</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>2000-8000</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>сейчас</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-04-06 08:08</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+          <t>2026-04-07 13:39</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1030</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1155412866</v>
+        <v>569692434</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>@Tremaska</t>
+          <t>@OlgaK_beauty</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>79260992058</t>
+          <t>79282589990</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1433,67 +1431,63 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>7-9</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>школа</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>формат</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Другое: Очень сложно даётся запоминание, понимание языка</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>акции</t>
+          <t>гайды</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>15000+</t>
+          <t>2000-8000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>результат</t>
+          <t>преподаватель</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>недавно</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-04-06 08:15</t>
+          <t>2026-04-06 12:42</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1007</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1288940419</v>
+        <v>590170268</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>@Tsimbalistova_Ekaterina</t>
+          <t>@anastasia_propuskova</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>79187643721</t>
+          <t>79817813120</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1508,34 +1502,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>СПб</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ребенок</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>7-9</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>школа</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>время</t>
-        </is>
-      </c>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>акции</t>
+          <t>гайды</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1550,30 +1540,30 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>давно</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-04-06 08:58</t>
+          <t>2026-04-06 08:28</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5186300541</v>
+        <v>687816500</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>@yuliguma</t>
+          <t>@EliaNazimovna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>79914348363</t>
+          <t>79872828487</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1583,7 +1573,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>✨18–24</t>
+          <t>✨35–44</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1593,30 +1583,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>путешествия</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>страх</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13-15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>рилсы</t>
+          <t>гайды</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>бесплатно</t>
+          <t>2000-8000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1626,30 +1620,30 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>давно</t>
+          <t>сейчас</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-04-06 07:57</t>
+          <t>2026-04-07 02:47</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>1003</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7286528532</v>
+        <v>700939186</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>@propuskstasy</t>
+          <t>@None</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>79930737358</t>
+          <t>79234240688</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1659,32 +1653,36 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>✨25–34</t>
+          <t>✨35–44</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>СПб</t>
+          <t>РФ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>переезд</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>страх</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Другое: Мы занимаемся</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>гайды</t>
@@ -1692,7 +1690,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9000-15000</t>
+          <t>2000-8000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1707,88 +1705,1828 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-04-06 08:44</t>
+          <t>2026-04-06 07:26</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>1011</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>754834257</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>@fil_katya</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>79098688511</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-04-06 12:13</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>774244434</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>@anastasioca</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>79857794744</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>игры</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Другое: Ничего не мешает ) занимаемся ) ищем более удобный формат</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:39</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>837194297</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>@Kiriyiki</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>79283280068</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:57</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>866643274</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>@voevodinamarina</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>79374049190</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:05</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>884855726</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>@Ann_I_N_Ann</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>79624493804</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>грамматика</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>9000-15000</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-04-07 13:50</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>895383725</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>@Anna_padalko1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>79286072201</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Другое: Уже занимается</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>9000-15000</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:04</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>928756491</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>@ekaterina121289</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:08</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>939809459</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>@mary_eeee</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>79031570547</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Другое: Уже занимаемся. Смущает скорость и качество обучения</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>15000+</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-04-06 19:20</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>964652565</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>@OM54551</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>разведка</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-04-08 11:42</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1013988143</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>79614866723</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>фильмы</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>мотивация</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-04-08 08:33</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1091599665</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>@ksusha_6311</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-04-09 14:27</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1155412866</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>@Tremaska</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>79260992058</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>15000+</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:15</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1214751654</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>@GlafiraShiryaeva31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>79647815531</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Другое: Ничего, мы занимаемся у Вас 😃😍</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:57</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1288940419</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>@Tsimbalistova_Ekaterina</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>79187643721</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:58</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1438203856</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>79061994609</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>13-15</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>школа</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-04-07 06:45</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1522177464</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>@NataliUdaltsova</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>79212801705</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>✨45+</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:02</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1540881359</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>@margo_riabchenko</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>79043746802</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>недавно</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-04-07 05:49</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1615923483</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>79283034334</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>формат</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-04-06 19:31</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5016107482</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>@DaryaSerazidinova</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>79272204309</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>говорение</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>сейчас</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-04-07 01:06</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5186300541</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>@yuliguma</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>79914348363</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>✨18–24</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>бесплатно</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:57</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5317054580</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>@marimops</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>79515890342</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>работа</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>деньги</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>рилсы</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>результат</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-04-06 12:27</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>7140259143</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>@seva_3535</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>✨35–44</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Мск</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ребенок</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>игры</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Другое: Уже занимаемся 🥰</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>акции</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2000-8000</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>преподаватель</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:46</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7286528532</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>@propuskstasy</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>79930737358</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>жен</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>✨25–34</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>СПб</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>взрослый</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>переезд</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>страх</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>гайды</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>9000-15000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>время</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>давно</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:44</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>8071127858</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>@nlo_cln</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>79969169607</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>муж</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>✨35–44</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>РФ</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>взрослый</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ребёнок</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>страх</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>чек-листы</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2000-8000</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>время</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>давно</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2026-04-06 09:13</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>1014</v>
-      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-04-06 15:38</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>8143298121</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>@None</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-04-06 12:27</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
